--- a/virtual-physics-lab/app/dl/NYJC_Q3_two_wires.xlsx
+++ b/virtual-physics-lab/app/dl/NYJC_Q3_two_wires.xlsx
@@ -17,7 +17,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="0.0"/>
+    <numFmt numFmtId="165" formatCode="0.000"/>
+  </numFmts>
   <fonts count="6">
     <font>
       <name val="Calibri"/>
@@ -91,7 +94,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -99,9 +102,11 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -674,71 +679,71 @@
       <c r="A6" s="5" t="n">
         <v>10</v>
       </c>
-      <c r="B6" s="5" t="n">
+      <c r="B6" s="6" t="n">
         <v>0.295</v>
       </c>
-      <c r="C6" s="6" t="n"/>
-      <c r="D6" s="6" t="n"/>
+      <c r="C6" s="7" t="n"/>
+      <c r="D6" s="7" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="5" t="n">
         <v>25</v>
       </c>
-      <c r="B7" s="5" t="n">
+      <c r="B7" s="6" t="n">
         <v>0.263</v>
       </c>
-      <c r="C7" s="6" t="n"/>
-      <c r="D7" s="6" t="n"/>
+      <c r="C7" s="7" t="n"/>
+      <c r="D7" s="7" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="5" t="n">
         <v>40</v>
       </c>
-      <c r="B8" s="5" t="n">
+      <c r="B8" s="6" t="n">
         <v>0.24</v>
       </c>
-      <c r="C8" s="6" t="n"/>
-      <c r="D8" s="6" t="n"/>
+      <c r="C8" s="7" t="n"/>
+      <c r="D8" s="7" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="5" t="n">
         <v>50</v>
       </c>
-      <c r="B9" s="5" t="n">
+      <c r="B9" s="6" t="n">
         <v>0.224</v>
       </c>
-      <c r="C9" s="6" t="n"/>
-      <c r="D9" s="6" t="n"/>
+      <c r="C9" s="7" t="n"/>
+      <c r="D9" s="7" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="5" t="n">
         <v>65</v>
       </c>
-      <c r="B10" s="5" t="n">
+      <c r="B10" s="6" t="n">
         <v>0.207</v>
       </c>
-      <c r="C10" s="6" t="n"/>
-      <c r="D10" s="6" t="n"/>
+      <c r="C10" s="7" t="n"/>
+      <c r="D10" s="7" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="5" t="n">
         <v>80</v>
       </c>
-      <c r="B11" s="5" t="n">
+      <c r="B11" s="6" t="n">
         <v>0.192</v>
       </c>
-      <c r="C11" s="6" t="n"/>
-      <c r="D11" s="6" t="n"/>
+      <c r="C11" s="7" t="n"/>
+      <c r="D11" s="7" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="5" t="n">
         <v>90</v>
       </c>
-      <c r="B12" s="5" t="n">
+      <c r="B12" s="6" t="n">
         <v>0.182</v>
       </c>
-      <c r="C12" s="6" t="n"/>
-      <c r="D12" s="6" t="n"/>
+      <c r="C12" s="7" t="n"/>
+      <c r="D12" s="7" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -818,27 +823,27 @@
       <c r="A6" s="5" t="n">
         <v>10</v>
       </c>
-      <c r="B6" s="5" t="n">
+      <c r="B6" s="6" t="n">
         <v>0.295</v>
       </c>
-      <c r="C6" s="7">
+      <c r="C6" s="8">
         <f>A6/100</f>
         <v/>
       </c>
-      <c r="D6" s="7">
+      <c r="D6" s="8">
         <f>1/B6</f>
         <v/>
       </c>
-      <c r="F6" s="5" t="inlineStr">
+      <c r="F6" s="9" t="inlineStr">
         <is>
           <t>P = gradient</t>
         </is>
       </c>
-      <c r="G6" s="7">
+      <c r="G6" s="8">
         <f>SLOPE(D6:D12,C6:C12)</f>
         <v/>
       </c>
-      <c r="H6" s="5" t="inlineStr">
+      <c r="H6" s="9" t="inlineStr">
         <is>
           <t>A⁻¹ m⁻¹</t>
         </is>
@@ -848,27 +853,27 @@
       <c r="A7" s="5" t="n">
         <v>25</v>
       </c>
-      <c r="B7" s="5" t="n">
+      <c r="B7" s="6" t="n">
         <v>0.263</v>
       </c>
-      <c r="C7" s="7">
+      <c r="C7" s="8">
         <f>A7/100</f>
         <v/>
       </c>
-      <c r="D7" s="7">
+      <c r="D7" s="8">
         <f>1/B7</f>
         <v/>
       </c>
-      <c r="F7" s="5" t="inlineStr">
+      <c r="F7" s="9" t="inlineStr">
         <is>
           <t>Q = intercept</t>
         </is>
       </c>
-      <c r="G7" s="7">
+      <c r="G7" s="8">
         <f>INTERCEPT(D6:D12,C6:C12)</f>
         <v/>
       </c>
-      <c r="H7" s="5" t="inlineStr">
+      <c r="H7" s="9" t="inlineStr">
         <is>
           <t>A⁻¹</t>
         </is>
@@ -878,40 +883,40 @@
       <c r="A8" s="5" t="n">
         <v>40</v>
       </c>
-      <c r="B8" s="5" t="n">
+      <c r="B8" s="6" t="n">
         <v>0.24</v>
       </c>
-      <c r="C8" s="7">
+      <c r="C8" s="8">
         <f>A8/100</f>
         <v/>
       </c>
-      <c r="D8" s="7">
+      <c r="D8" s="8">
         <f>1/B8</f>
         <v/>
       </c>
-      <c r="F8" s="5" t="inlineStr">
+      <c r="F8" s="9" t="inlineStr">
         <is>
           <t>d_G/d_F = √(1 + LP/Q)</t>
         </is>
       </c>
-      <c r="G8" s="7">
+      <c r="G8" s="8">
         <f>SQRT(1+SLOPE(D6:D12,C6:C12)/INTERCEPT(D6:D12,C6:C12))</f>
         <v/>
       </c>
-      <c r="H8" s="5" t="inlineStr"/>
+      <c r="H8" s="9" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="5" t="n">
         <v>50</v>
       </c>
-      <c r="B9" s="5" t="n">
+      <c r="B9" s="6" t="n">
         <v>0.224</v>
       </c>
-      <c r="C9" s="7">
+      <c r="C9" s="8">
         <f>A9/100</f>
         <v/>
       </c>
-      <c r="D9" s="7">
+      <c r="D9" s="8">
         <f>1/B9</f>
         <v/>
       </c>
@@ -920,14 +925,14 @@
       <c r="A10" s="5" t="n">
         <v>65</v>
       </c>
-      <c r="B10" s="5" t="n">
+      <c r="B10" s="6" t="n">
         <v>0.207</v>
       </c>
-      <c r="C10" s="7">
+      <c r="C10" s="8">
         <f>A10/100</f>
         <v/>
       </c>
-      <c r="D10" s="7">
+      <c r="D10" s="8">
         <f>1/B10</f>
         <v/>
       </c>
@@ -936,14 +941,14 @@
       <c r="A11" s="5" t="n">
         <v>80</v>
       </c>
-      <c r="B11" s="5" t="n">
+      <c r="B11" s="6" t="n">
         <v>0.192</v>
       </c>
-      <c r="C11" s="7">
+      <c r="C11" s="8">
         <f>A11/100</f>
         <v/>
       </c>
-      <c r="D11" s="7">
+      <c r="D11" s="8">
         <f>1/B11</f>
         <v/>
       </c>
@@ -952,14 +957,14 @@
       <c r="A12" s="5" t="n">
         <v>90</v>
       </c>
-      <c r="B12" s="5" t="n">
+      <c r="B12" s="6" t="n">
         <v>0.182</v>
       </c>
-      <c r="C12" s="7">
+      <c r="C12" s="8">
         <f>A12/100</f>
         <v/>
       </c>
-      <c r="D12" s="7">
+      <c r="D12" s="8">
         <f>1/B12</f>
         <v/>
       </c>
